--- a/excel/output_stats_vfvv/covariance/EfficiencyStats.xlsx
+++ b/excel/output_stats_vfvv/covariance/EfficiencyStats.xlsx
@@ -499,16 +499,16 @@
         <v>44.7656</v>
       </c>
       <c r="F2" t="n">
-        <v>355.51</v>
+        <v>356.67</v>
       </c>
       <c r="G2" t="n">
-        <v>357.83</v>
+        <v>359.16</v>
       </c>
       <c r="H2" t="n">
-        <v>345.426</v>
+        <v>346.177</v>
       </c>
       <c r="I2" t="n">
-        <v>344.471</v>
+        <v>345.268</v>
       </c>
       <c r="J2" t="n">
         <v>11393400000</v>
